--- a/examples/07_WO3_on_BK7_60deg.xlsx
+++ b/examples/07_WO3_on_BK7_60deg.xlsx
@@ -4326,7 +4326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4396,100 +4396,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>60</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>850</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±5</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>350 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/07_WO3_on_BK7_60deg.xlsx
+++ b/examples/07_WO3_on_BK7_60deg.xlsx
@@ -478,16 +478,16 @@
         <v>350</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.7608</v>
+        <v>6.7738</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>192.4054</v>
+        <v>192.617</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.0438</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.412</v>
+        <v>0.4113</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>352</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.0457</v>
+        <v>5.0103</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>166.6648</v>
+        <v>166.7777</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0434</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.549</v>
+        <v>0.5528999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +512,16 @@
         <v>354</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.9966</v>
+        <v>7.0041</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>140.9128</v>
+        <v>140.6929</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.043</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3915</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="5">
@@ -529,16 +529,16 @@
         <v>356</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10.133</v>
+        <v>10.1667</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>143.0682</v>
+        <v>143.0743</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0427</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.2708</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="6">
@@ -546,16 +546,16 @@
         <v>358</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>12.4924</v>
+        <v>12.5151</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>152.2369</v>
+        <v>152.3034</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0423</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2208</v>
+        <v>0.2204</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         <v>360</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.8345</v>
+        <v>13.8455</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>162.6787</v>
+        <v>162.7265</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0419</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1984</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="8">
@@ -580,16 +580,16 @@
         <v>362</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14.3811</v>
+        <v>14.387</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173.9204</v>
+        <v>173.9328</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0415</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1894</v>
+        <v>0.1893</v>
       </c>
     </row>
     <row r="9">
@@ -597,16 +597,16 @@
         <v>364</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>14.292</v>
+        <v>14.2984</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>185.9381</v>
+        <v>185.9094</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0412</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1895</v>
+        <v>0.1894</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         <v>366</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>13.3601</v>
+        <v>13.3726</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>198.2531</v>
+        <v>198.171</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0408</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1986</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="11">
@@ -631,16 +631,16 @@
         <v>368</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11.9426</v>
+        <v>11.9687</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>212.2926</v>
+        <v>212.1258</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0404</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.2205</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         <v>370</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>9.490399999999999</v>
+        <v>9.539199999999999</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>230.0879</v>
+        <v>229.7721</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0401</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.2696</v>
+        <v>0.2683</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>372</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>6.2133</v>
+        <v>6.2664</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>257.2336</v>
+        <v>256.709</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0397</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.4102</v>
+        <v>0.4067</v>
       </c>
     </row>
     <row r="14">
@@ -682,10 +682,10 @@
         <v>374</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.0568</v>
+        <v>2.9853</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>343.8872</v>
+        <v>343.0905</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0394</v>
@@ -699,16 +699,16 @@
         <v>376</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5.9035</v>
+        <v>5.9366</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>79.62090000000001</v>
+        <v>79.96550000000001</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.039</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.4109</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>378</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9.5602</v>
+        <v>9.613</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>109.7509</v>
+        <v>110.1151</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0387</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.2588</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="17">
@@ -733,16 +733,16 @@
         <v>380</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11.88</v>
+        <v>11.9093</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>128.5888</v>
+        <v>128.8066</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0383</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.209</v>
+        <v>0.2085</v>
       </c>
     </row>
     <row r="18">
@@ -750,16 +750,16 @@
         <v>382</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>13.3187</v>
+        <v>13.3328</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>142.9877</v>
+        <v>143.1057</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.038</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.1861</v>
+        <v>0.1859</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         <v>384</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>14.2419</v>
+        <v>14.2486</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>154.241</v>
+        <v>154.3039</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0376</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.1738</v>
+        <v>0.1737</v>
       </c>
     </row>
     <row r="20">
@@ -784,10 +784,10 @@
         <v>386</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>14.6815</v>
+        <v>14.6849</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>164.725</v>
+        <v>164.7545</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0373</v>
@@ -801,10 +801,10 @@
         <v>388</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>14.7375</v>
+        <v>14.7399</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>174.5181</v>
+        <v>174.5247</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.037</v>
@@ -818,10 +818,10 @@
         <v>390</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>14.627</v>
+        <v>14.6298</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>184.3081</v>
+        <v>184.2954</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0366</v>
@@ -835,16 +835,16 @@
         <v>392</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>14.047</v>
+        <v>14.0513</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>193.8688</v>
+        <v>193.8362</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0363</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.1693</v>
+        <v>0.1692</v>
       </c>
     </row>
     <row r="24">
@@ -852,16 +852,16 @@
         <v>394</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13.3345</v>
+        <v>13.3416</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>203.7211</v>
+        <v>203.6638</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.036</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.1769</v>
+        <v>0.1768</v>
       </c>
     </row>
     <row r="25">
@@ -869,16 +869,16 @@
         <v>396</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>12.1657</v>
+        <v>12.1771</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>214.5413</v>
+        <v>214.4485</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0356</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1894</v>
+        <v>0.1892</v>
       </c>
     </row>
     <row r="26">
@@ -886,16 +886,16 @@
         <v>398</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10.8466</v>
+        <v>10.8642</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>227.0196</v>
+        <v>226.8716</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0353</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.2095</v>
+        <v>0.2091</v>
       </c>
     </row>
     <row r="27">
@@ -903,16 +903,16 @@
         <v>400</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>9.1814</v>
+        <v>9.206300000000001</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>242.5175</v>
+        <v>242.2848</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.035</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.2438</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="28">
@@ -920,16 +920,16 @@
         <v>402</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7.1045</v>
+        <v>7.1301</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>265.838</v>
+        <v>265.4921</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0347</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.3097</v>
+        <v>0.3087</v>
       </c>
     </row>
     <row r="29">
@@ -940,7 +940,7 @@
         <v>5.0019</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>305.1501</v>
+        <v>304.7512</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0344</v>
@@ -954,16 +954,16 @@
         <v>406</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4.2745</v>
+        <v>4.2531</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>11.4159</v>
+        <v>11.4038</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.0341</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.4968</v>
+        <v>0.4992</v>
       </c>
     </row>
     <row r="31">
@@ -971,16 +971,16 @@
         <v>408</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>6.0313</v>
+        <v>6.0428</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>64.6724</v>
+        <v>64.94840000000001</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0337</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.3515</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="32">
@@ -988,16 +988,16 @@
         <v>410</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8.1793</v>
+        <v>8.2026</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>93.45740000000001</v>
+        <v>93.71510000000001</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0334</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.2596</v>
+        <v>0.2589</v>
       </c>
     </row>
     <row r="33">
@@ -1005,16 +1005,16 @@
         <v>412</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>9.874499999999999</v>
+        <v>9.892899999999999</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>111.9903</v>
+        <v>112.1719</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0331</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.2148</v>
+        <v>0.2144</v>
       </c>
     </row>
     <row r="34">
@@ -1022,16 +1022,16 @@
         <v>414</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>11.1542</v>
+        <v>11.1662</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>125.8658</v>
+        <v>125.9836</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.19</v>
+        <v>0.1898</v>
       </c>
     </row>
     <row r="35">
@@ -1039,16 +1039,16 @@
         <v>416</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>12.1115</v>
+        <v>12.1189</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>136.6293</v>
+        <v>136.7051</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0325</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1746</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="36">
@@ -1056,16 +1056,16 @@
         <v>418</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>12.7799</v>
+        <v>12.7844</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>145.7254</v>
+        <v>145.7745</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0322</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.1643</v>
+        <v>0.1642</v>
       </c>
     </row>
     <row r="37">
@@ -1073,16 +1073,16 @@
         <v>420</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>13.2352</v>
+        <v>13.238</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>153.9629</v>
+        <v>153.9943</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.1572</v>
+        <v>0.1571</v>
       </c>
     </row>
     <row r="38">
@@ -1090,10 +1090,10 @@
         <v>422</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13.5307</v>
+        <v>13.5324</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>161.9305</v>
+        <v>161.9496</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0316</v>
@@ -1107,10 +1107,10 @@
         <v>424</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>13.7485</v>
+        <v>13.7498</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>169.1883</v>
+        <v>169.1979</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0313</v>
@@ -1124,16 +1124,16 @@
         <v>426</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13.7123</v>
+        <v>13.7134</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>176.4466</v>
+        <v>176.4484</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.148</v>
+        <v>0.1479</v>
       </c>
     </row>
     <row r="41">
@@ -1141,10 +1141,10 @@
         <v>428</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>13.56</v>
+        <v>13.5612</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>183.3782</v>
+        <v>183.3727</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0308</v>
@@ -1158,10 +1158,10 @@
         <v>430</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>13.3493</v>
+        <v>13.3509</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>190.6694</v>
+        <v>190.6566</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0305</v>
@@ -1175,10 +1175,10 @@
         <v>432</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>12.9213</v>
+        <v>12.9235</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>197.6827</v>
+        <v>197.6617</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.0302</v>
@@ -1192,10 +1192,10 @@
         <v>434</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>12.3616</v>
+        <v>12.3648</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>205.3393</v>
+        <v>205.3083</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0299</v>
@@ -1209,10 +1209,10 @@
         <v>436</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>11.7058</v>
+        <v>11.7103</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>213.45</v>
+        <v>213.4059</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0297</v>
@@ -1226,16 +1226,16 @@
         <v>438</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>10.9493</v>
+        <v>10.9555</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>222.2036</v>
+        <v>222.1419</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.1728</v>
+        <v>0.1727</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         <v>440</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>10.0722</v>
+        <v>10.0805</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>232.1202</v>
+        <v>232.034</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.1858</v>
+        <v>0.1856</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>442</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>9.0167</v>
+        <v>9.027100000000001</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>244.0067</v>
+        <v>243.8872</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.2047</v>
+        <v>0.2044</v>
       </c>
     </row>
     <row r="49">
@@ -1277,16 +1277,16 @@
         <v>444</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7.7921</v>
+        <v>7.8037</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>259.7975</v>
+        <v>259.6358</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.2332</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="50">
@@ -1294,16 +1294,16 @@
         <v>446</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>6.4322</v>
+        <v>6.4412</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>279.8706</v>
+        <v>279.671</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0283</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.2774</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="51">
@@ -1311,16 +1311,16 @@
         <v>448</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5.2685</v>
+        <v>5.2683</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>309.6967</v>
+        <v>309.4992</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0281</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.3381</v>
+        <v>0.3382</v>
       </c>
     </row>
     <row r="52">
@@ -1328,16 +1328,16 @@
         <v>450</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4.6105</v>
+        <v>4.6016</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>350.9577</v>
+        <v>350.8814</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0278</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.3763</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="53">
@@ -1345,16 +1345,16 @@
         <v>452</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5.1887</v>
+        <v>5.1851</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>32.7892</v>
+        <v>32.8794</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.0275</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.3363</v>
+        <v>0.3365</v>
       </c>
     </row>
     <row r="54">
@@ -1362,16 +1362,16 @@
         <v>454</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6.3816</v>
+        <v>6.3875</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>63.6203</v>
+        <v>63.7728</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0273</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.2714</v>
+        <v>0.2711</v>
       </c>
     </row>
     <row r="55">
@@ -1379,16 +1379,16 @@
         <v>456</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7.6523</v>
+        <v>7.6621</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>84.8986</v>
+        <v>85.045</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.2245</v>
+        <v>0.2242</v>
       </c>
     </row>
     <row r="56">
@@ -1396,16 +1396,16 @@
         <v>458</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>8.8408</v>
+        <v>8.850199999999999</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>100.9403</v>
+        <v>101.0581</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0268</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.1945</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="57">
@@ -1413,16 +1413,16 @@
         <v>460</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>9.817600000000001</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>112.8808</v>
+        <v>112.9696</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0266</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.1749</v>
+        <v>0.1748</v>
       </c>
     </row>
     <row r="58">
@@ -1430,16 +1430,16 @@
         <v>462</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>10.4612</v>
+        <v>10.4666</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>122.8848</v>
+        <v>122.9498</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0263</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.1613</v>
+        <v>0.1612</v>
       </c>
     </row>
     <row r="59">
@@ -1447,16 +1447,16 @@
         <v>464</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>11.1299</v>
+        <v>11.1338</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>131.6893</v>
+        <v>131.7365</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0261</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.1513</v>
+        <v>0.1512</v>
       </c>
     </row>
     <row r="60">
@@ -1464,10 +1464,10 @@
         <v>466</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>11.6156</v>
+        <v>11.6184</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>138.943</v>
+        <v>138.9776</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0258</v>
@@ -1481,16 +1481,16 @@
         <v>468</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>12.0113</v>
+        <v>12.0133</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>145.7102</v>
+        <v>145.7355</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0256</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.1379</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="62">
@@ -1498,10 +1498,10 @@
         <v>470</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>12.4141</v>
+        <v>12.4155</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>151.7228</v>
+        <v>151.7412</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0254</v>
@@ -1515,10 +1515,10 @@
         <v>472</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>12.627</v>
+        <v>12.628</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>157.7013</v>
+        <v>157.7144</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0251</v>
@@ -1532,10 +1532,10 @@
         <v>474</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>12.7743</v>
+        <v>12.775</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>163.1304</v>
+        <v>163.1394</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0249</v>
@@ -1549,10 +1549,10 @@
         <v>476</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>12.8864</v>
+        <v>12.887</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>168.7073</v>
+        <v>168.7128</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0247</v>
@@ -1566,10 +1566,10 @@
         <v>478</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>12.8909</v>
+        <v>12.8914</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>174.2656</v>
+        <v>174.268</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0245</v>
@@ -1583,10 +1583,10 @@
         <v>480</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>12.8496</v>
+        <v>12.8501</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>179.3107</v>
+        <v>179.3103</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0242</v>
@@ -1600,10 +1600,10 @@
         <v>482</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>12.729</v>
+        <v>12.7296</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>184.5728</v>
+        <v>184.5696</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.024</v>
@@ -1617,10 +1617,10 @@
         <v>484</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>12.5675</v>
+        <v>12.5682</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>189.8393</v>
+        <v>189.8334</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0238</v>
@@ -1634,10 +1634,10 @@
         <v>486</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>12.3427</v>
+        <v>12.3436</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>195.3604</v>
+        <v>195.3515</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0236</v>
@@ -1651,10 +1651,10 @@
         <v>488</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>12.077</v>
+        <v>12.0781</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>200.7353</v>
+        <v>200.723</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.0234</v>
@@ -1668,10 +1668,10 @@
         <v>490</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>11.7383</v>
+        <v>11.7397</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>206.0258</v>
+        <v>206.0098</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0232</v>
@@ -1685,10 +1685,10 @@
         <v>492</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>11.2995</v>
+        <v>11.3013</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>211.9496</v>
+        <v>211.929</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.023</v>
@@ -1702,10 +1702,10 @@
         <v>494</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>10.864</v>
+        <v>10.8663</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>218.215</v>
+        <v>218.1889</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0228</v>
@@ -1719,10 +1719,10 @@
         <v>496</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>10.3513</v>
+        <v>10.3541</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>224.9839</v>
+        <v>224.9507</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0226</v>
@@ -1736,16 +1736,16 @@
         <v>498</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>9.8383</v>
+        <v>9.841699999999999</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>232.1889</v>
+        <v>232.147</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0224</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.1469</v>
+        <v>0.1468</v>
       </c>
     </row>
     <row r="77">
@@ -1753,16 +1753,16 @@
         <v>500</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>9.215299999999999</v>
+        <v>9.2194</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>240.2515</v>
+        <v>240.1987</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0222</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.1551</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="78">
@@ -1770,16 +1770,16 @@
         <v>502</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>8.481999999999999</v>
+        <v>8.486599999999999</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>249.697</v>
+        <v>249.6312</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.022</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.1657</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="79">
@@ -1787,16 +1787,16 @@
         <v>504</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7.7216</v>
+        <v>7.7264</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>261.1424</v>
+        <v>261.0621</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0218</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.1797</v>
+        <v>0.1796</v>
       </c>
     </row>
     <row r="80">
@@ -1804,16 +1804,16 @@
         <v>506</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6.9446</v>
+        <v>6.9489</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>274.7616</v>
+        <v>274.6676</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0216</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.1981</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="81">
@@ -1821,16 +1821,16 @@
         <v>508</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6.1649</v>
+        <v>6.1675</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>291.9808</v>
+        <v>291.8795</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0215</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.2211</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="82">
@@ -1838,10 +1838,10 @@
         <v>510</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5.4387</v>
+        <v>5.4386</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>313.6473</v>
+        <v>313.5551</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0213</v>
@@ -1855,16 +1855,16 @@
         <v>512</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>5.1028</v>
+        <v>5.0999</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>338.9876</v>
+        <v>338.9319</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0211</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.2637</v>
+        <v>0.2638</v>
       </c>
     </row>
     <row r="84">
@@ -1872,16 +1872,16 @@
         <v>514</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>5.0528</v>
+        <v>5.0495</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>7.0464</v>
+        <v>7.0479</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0209</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.261</v>
+        <v>0.2612</v>
       </c>
     </row>
     <row r="85">
@@ -1889,10 +1889,10 @@
         <v>516</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5.4975</v>
+        <v>5.4964</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>32.8526</v>
+        <v>32.9026</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0207</v>
@@ -1906,16 +1906,16 @@
         <v>518</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>6.135</v>
+        <v>6.1367</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>53.9107</v>
+        <v>53.9845</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0206</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.2113</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="87">
@@ -1923,16 +1923,16 @@
         <v>520</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6.9624</v>
+        <v>6.9659</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>71.42</v>
+        <v>71.4979</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.1867</v>
+        <v>0.1866</v>
       </c>
     </row>
     <row r="88">
@@ -1940,16 +1940,16 @@
         <v>522</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>7.6987</v>
+        <v>7.7029</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>85.36499999999999</v>
+        <v>85.4367</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0202</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.1675</v>
+        <v>0.1674</v>
       </c>
     </row>
     <row r="89">
@@ -1957,16 +1957,16 @@
         <v>524</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>8.4078</v>
+        <v>8.411799999999999</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>96.6276</v>
+        <v>96.6891</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0201</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.1529</v>
+        <v>0.1528</v>
       </c>
     </row>
     <row r="90">
@@ -1974,16 +1974,16 @@
         <v>526</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>8.976000000000001</v>
+        <v>8.9795</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>106.0392</v>
+        <v>106.0901</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0199</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.1418</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="91">
@@ -1991,10 +1991,10 @@
         <v>528</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>9.539300000000001</v>
+        <v>9.542199999999999</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>113.9198</v>
+        <v>113.9612</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0198</v>
@@ -2008,10 +2008,10 @@
         <v>530</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>9.972799999999999</v>
+        <v>9.975199999999999</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>121.3206</v>
+        <v>121.3538</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0196</v>
@@ -2025,10 +2025,10 @@
         <v>532</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>10.3821</v>
+        <v>10.384</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>127.4066</v>
+        <v>127.4332</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0195</v>
@@ -2042,10 +2042,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>10.7734</v>
+        <v>10.7749</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>133.0844</v>
+        <v>133.1058</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0193</v>
@@ -2059,10 +2059,10 @@
         <v>536</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>11.0471</v>
+        <v>11.0483</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>138.26</v>
+        <v>138.2772</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0192</v>
@@ -2076,16 +2076,16 @@
         <v>538</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>11.3059</v>
+        <v>11.3068</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>143.1496</v>
+        <v>143.1634</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.019</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.1087</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="97">
@@ -2093,16 +2093,16 @@
         <v>540</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>11.538</v>
+        <v>11.5387</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>147.8408</v>
+        <v>147.8519</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0189</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0.1059</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="98">
@@ -2110,10 +2110,10 @@
         <v>542</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>11.7125</v>
+        <v>11.7131</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>152.2301</v>
+        <v>152.2389</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0187</v>
@@ -2127,10 +2127,10 @@
         <v>544</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>11.8991</v>
+        <v>11.8996</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>156.4551</v>
+        <v>156.4621</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.0186</v>
@@ -2144,10 +2144,10 @@
         <v>546</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>11.9827</v>
+        <v>11.983</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>160.713</v>
+        <v>160.7184</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0185</v>
@@ -2161,10 +2161,10 @@
         <v>548</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>12.1051</v>
+        <v>12.1054</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>164.6435</v>
+        <v>164.6476</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0183</v>
@@ -2178,10 +2178,10 @@
         <v>550</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>12.1594</v>
+        <v>12.1597</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>168.4111</v>
+        <v>168.414</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0182</v>
@@ -2195,10 +2195,10 @@
         <v>552</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>12.1717</v>
+        <v>12.1719</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>172.2723</v>
+        <v>172.274</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0181</v>
@@ -2212,10 +2212,10 @@
         <v>554</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>12.1686</v>
+        <v>12.1688</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>176.1325</v>
+        <v>176.1332</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0179</v>
@@ -2229,10 +2229,10 @@
         <v>556</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>12.1482</v>
+        <v>12.1484</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>179.9446</v>
+        <v>179.9443</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0178</v>
@@ -2246,10 +2246,10 @@
         <v>558</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>12.093</v>
+        <v>12.0932</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>183.7751</v>
+        <v>183.7739</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0177</v>
@@ -2263,10 +2263,10 @@
         <v>560</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>11.9719</v>
+        <v>11.9722</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>187.445</v>
+        <v>187.4429</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0176</v>
@@ -2280,10 +2280,10 @@
         <v>562</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>11.8672</v>
+        <v>11.8675</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>191.2096</v>
+        <v>191.2065</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0175</v>
@@ -2297,16 +2297,16 @@
         <v>564</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>11.7404</v>
+        <v>11.7408</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>194.9672</v>
+        <v>194.9631</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0174</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.096</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="110">
@@ -2314,10 +2314,10 @@
         <v>566</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>11.5377</v>
+        <v>11.5382</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>198.5041</v>
+        <v>198.499</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0173</v>
@@ -2331,10 +2331,10 @@
         <v>568</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>11.3501</v>
+        <v>11.3506</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>202.6621</v>
+        <v>202.6558</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0172</v>
@@ -2348,10 +2348,10 @@
         <v>570</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>11.1508</v>
+        <v>11.1514</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>206.8102</v>
+        <v>206.8027</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.017</v>
@@ -2365,10 +2365,10 @@
         <v>572</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>10.9028</v>
+        <v>10.9034</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>210.8037</v>
+        <v>210.7947</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0169</v>
@@ -2382,10 +2382,10 @@
         <v>574</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>10.6358</v>
+        <v>10.6366</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>214.9725</v>
+        <v>214.9619</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0168</v>
@@ -2399,10 +2399,10 @@
         <v>576</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>10.4034</v>
+        <v>10.4043</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>219.4344</v>
+        <v>219.4219</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0168</v>
@@ -2416,10 +2416,10 @@
         <v>578</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>10.0431</v>
+        <v>10.0441</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>224.0057</v>
+        <v>223.991</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0167</v>
@@ -2433,10 +2433,10 @@
         <v>580</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>9.738899999999999</v>
+        <v>9.7401</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>229.0352</v>
+        <v>229.018</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0166</v>
@@ -2450,10 +2450,10 @@
         <v>582</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>9.428100000000001</v>
+        <v>9.429500000000001</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>234.194</v>
+        <v>234.1739</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0165</v>
@@ -2467,10 +2467,10 @@
         <v>584</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>9.062200000000001</v>
+        <v>9.063800000000001</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>239.7332</v>
+        <v>239.7098</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0164</v>
@@ -2484,10 +2484,10 @@
         <v>586</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>8.622999999999999</v>
+        <v>8.6248</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>246.2806</v>
+        <v>246.2534</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0163</v>
@@ -2501,10 +2501,10 @@
         <v>588</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>8.220499999999999</v>
+        <v>8.222300000000001</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>252.9924</v>
+        <v>252.9611</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.0162</v>
@@ -2518,10 +2518,10 @@
         <v>590</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>7.7915</v>
+        <v>7.7934</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>260.4554</v>
+        <v>260.4199</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.0162</v>
@@ -2535,16 +2535,16 @@
         <v>592</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7.3227</v>
+        <v>7.3246</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>269.3146</v>
+        <v>269.2748</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.0161</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.1399</v>
+        <v>0.1398</v>
       </c>
     </row>
     <row r="124">
@@ -2552,16 +2552,16 @@
         <v>594</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6.8449</v>
+        <v>6.8466</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>278.8033</v>
+        <v>278.76</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.016</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.1486</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="125">
@@ -2569,10 +2569,10 @@
         <v>596</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6.3654</v>
+        <v>6.3666</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>289.8243</v>
+        <v>289.7793</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.0159</v>
@@ -2586,10 +2586,10 @@
         <v>598</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5.9476</v>
+        <v>5.9482</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>303.0543</v>
+        <v>303.0103</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.0159</v>
@@ -2603,10 +2603,10 @@
         <v>600</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>5.5963</v>
+        <v>5.5961</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>317.7547</v>
+        <v>317.7161</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.0158</v>
@@ -2620,10 +2620,10 @@
         <v>602</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5.3722</v>
+        <v>5.3713</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>333.7381</v>
+        <v>333.7102</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.0157</v>
@@ -2637,10 +2637,10 @@
         <v>604</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>5.2673</v>
+        <v>5.2661</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>351.3069</v>
+        <v>351.2943</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.0157</v>
@@ -2654,10 +2654,10 @@
         <v>606</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>5.3181</v>
+        <v>5.317</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>8.710900000000001</v>
+        <v>8.7149</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.0156</v>
@@ -2671,10 +2671,10 @@
         <v>608</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5.5308</v>
+        <v>5.5302</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>25.1814</v>
+        <v>25.1998</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.0156</v>
@@ -2688,10 +2688,10 @@
         <v>610</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>5.8689</v>
+        <v>5.869</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>40.0314</v>
+        <v>40.0598</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.0155</v>
@@ -2705,10 +2705,10 @@
         <v>612</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>6.2973</v>
+        <v>6.298</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>53.4309</v>
+        <v>53.4647</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.0155</v>
@@ -2722,10 +2722,10 @@
         <v>614</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>6.7222</v>
+        <v>6.7234</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>64.5971</v>
+        <v>64.6326</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.0154</v>
@@ -2739,10 +2739,10 @@
         <v>616</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7.1836</v>
+        <v>7.1851</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>75</v>
+        <v>75.0347</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.0154</v>
@@ -2756,10 +2756,10 @@
         <v>618</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>7.5971</v>
+        <v>7.5987</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>84.3459</v>
+        <v>84.37820000000001</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.0153</v>
@@ -2773,10 +2773,10 @@
         <v>620</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7.9928</v>
+        <v>7.9944</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>91.9572</v>
+        <v>91.98650000000001</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.0153</v>
@@ -2790,10 +2790,10 @@
         <v>622</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>8.3681</v>
+        <v>8.3696</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>98.7996</v>
+        <v>98.82559999999999</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.0153</v>
@@ -2807,10 +2807,10 @@
         <v>624</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>8.756500000000001</v>
+        <v>8.757899999999999</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>104.912</v>
+        <v>104.9348</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.0152</v>
@@ -2824,10 +2824,10 @@
         <v>626</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>9.0337</v>
+        <v>9.0349</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>110.4904</v>
+        <v>110.5102</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.0152</v>
@@ -2841,10 +2841,10 @@
         <v>628</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>9.3301</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>115.6333</v>
+        <v>115.6505</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.0152</v>
@@ -2858,10 +2858,10 @@
         <v>630</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>9.589700000000001</v>
+        <v>9.5906</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>120.6645</v>
+        <v>120.6793</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.0151</v>
@@ -2875,10 +2875,10 @@
         <v>632</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>9.857100000000001</v>
+        <v>9.857900000000001</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>124.9443</v>
+        <v>124.9571</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.0151</v>
@@ -2892,10 +2892,10 @@
         <v>634</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>10.083</v>
+        <v>10.0837</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>128.9374</v>
+        <v>128.9484</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.0151</v>
@@ -2909,16 +2909,16 @@
         <v>636</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>10.2725</v>
+        <v>10.2731</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>132.7773</v>
+        <v>132.7868</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -2926,10 +2926,10 @@
         <v>638</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>10.4625</v>
+        <v>10.463</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>136.4127</v>
+        <v>136.4209</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
@@ -2943,10 +2943,10 @@
         <v>640</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>10.6615</v>
+        <v>10.6619</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>139.7159</v>
+        <v>139.723</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
@@ -2960,10 +2960,10 @@
         <v>642</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>10.7913</v>
+        <v>10.7917</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>143.1847</v>
+        <v>143.1909</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
@@ -2977,10 +2977,10 @@
         <v>644</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>10.9414</v>
+        <v>10.9417</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>146.2091</v>
+        <v>146.2144</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,10 +2994,10 @@
         <v>646</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>11.0441</v>
+        <v>11.0443</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>149.2513</v>
+        <v>149.2559</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
@@ -3011,10 +3011,10 @@
         <v>648</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>11.2278</v>
+        <v>11.228</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>152.2315</v>
+        <v>152.2354</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
@@ -3028,10 +3028,10 @@
         <v>650</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>11.2846</v>
+        <v>11.2848</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>155.2015</v>
+        <v>155.2048</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
@@ -3045,10 +3045,10 @@
         <v>652</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>11.3698</v>
+        <v>11.3699</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>157.9762</v>
+        <v>157.979</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3062,10 +3062,10 @@
         <v>654</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>11.4368</v>
+        <v>11.437</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>160.6758</v>
+        <v>160.6782</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
@@ -3079,10 +3079,10 @@
         <v>656</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>11.4977</v>
+        <v>11.4978</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>163.3848</v>
+        <v>163.3868</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
@@ -3096,10 +3096,10 @@
         <v>658</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>11.5306</v>
+        <v>11.5308</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>166.0952</v>
+        <v>166.0968</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
@@ -3113,10 +3113,10 @@
         <v>660</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>11.5622</v>
+        <v>11.5623</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>168.7004</v>
+        <v>168.7016</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
@@ -3130,10 +3130,10 @@
         <v>662</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>11.6084</v>
+        <v>11.6085</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>171.3287</v>
+        <v>171.3296</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3147,10 +3147,10 @@
         <v>664</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>11.5832</v>
+        <v>11.5833</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>173.9763</v>
+        <v>173.9769</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
@@ -3164,10 +3164,10 @@
         <v>666</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>11.6085</v>
+        <v>11.6086</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>176.3818</v>
+        <v>176.3821</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
@@ -3181,7 +3181,7 @@
         <v>668</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>11.5465</v>
+        <v>11.5466</v>
       </c>
       <c r="C161" s="2" t="n">
         <v>179.0792</v>
@@ -3198,10 +3198,10 @@
         <v>670</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>11.5695</v>
+        <v>11.5696</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>181.6176</v>
+        <v>181.6174</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3215,10 +3215,10 @@
         <v>672</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>11.492</v>
+        <v>11.4921</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>184.1157</v>
+        <v>184.1152</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3232,10 +3232,10 @@
         <v>674</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>11.4525</v>
+        <v>11.4526</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>186.6438</v>
+        <v>186.6431</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3249,10 +3249,10 @@
         <v>676</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>11.3892</v>
+        <v>11.3893</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>189.1258</v>
+        <v>189.1248</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3266,10 +3266,10 @@
         <v>678</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>11.3401</v>
+        <v>11.3402</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>191.6118</v>
+        <v>191.6105</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
@@ -3283,10 +3283,10 @@
         <v>680</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>11.2262</v>
+        <v>11.2263</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>194.0134</v>
+        <v>194.0118</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3300,10 +3300,10 @@
         <v>682</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>11.1548</v>
+        <v>11.1549</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>196.7614</v>
+        <v>196.7596</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>684</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>11.0349</v>
+        <v>11.0351</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>199.2686</v>
+        <v>199.2664</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>686</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>10.9529</v>
+        <v>10.9531</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>201.8677</v>
+        <v>201.8653</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3351,10 +3351,10 @@
         <v>688</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>10.856</v>
+        <v>10.8562</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>204.5112</v>
+        <v>204.5084</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3368,10 +3368,10 @@
         <v>690</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>10.6824</v>
+        <v>10.6826</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>207.1594</v>
+        <v>207.1563</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3385,10 +3385,10 @@
         <v>692</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>10.6019</v>
+        <v>10.6021</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>209.8521</v>
+        <v>209.8486</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3402,10 +3402,10 @@
         <v>694</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>10.4226</v>
+        <v>10.4229</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>212.5461</v>
+        <v>212.5421</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>696</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>10.2955</v>
+        <v>10.2958</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>215.2866</v>
+        <v>215.2823</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3436,10 +3436,10 @@
         <v>698</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>10.1354</v>
+        <v>10.1357</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>218.4267</v>
+        <v>218.4219</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3453,10 +3453,10 @@
         <v>700</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>9.985200000000001</v>
+        <v>9.9855</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>221.2728</v>
+        <v>221.2675</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3470,10 +3470,10 @@
         <v>702</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>9.7483</v>
+        <v>9.748699999999999</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>224.0594</v>
+        <v>224.0535</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3487,10 +3487,10 @@
         <v>704</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>9.5929</v>
+        <v>9.593299999999999</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>227.2532</v>
+        <v>227.2466</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3504,10 +3504,10 @@
         <v>706</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>9.4329</v>
+        <v>9.433400000000001</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>230.578</v>
+        <v>230.5708</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3521,10 +3521,10 @@
         <v>708</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>9.2026</v>
+        <v>9.203099999999999</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>233.9995</v>
+        <v>233.9916</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3538,10 +3538,10 @@
         <v>710</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>9.0382</v>
+        <v>9.0388</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>237.721</v>
+        <v>237.7122</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3555,10 +3555,10 @@
         <v>712</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>8.8081</v>
+        <v>8.8087</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>241.4355</v>
+        <v>241.4259</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3572,10 +3572,10 @@
         <v>714</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>8.579599999999999</v>
+        <v>8.5802</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>244.923</v>
+        <v>244.9124</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3589,10 +3589,10 @@
         <v>716</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>8.34</v>
+        <v>8.3406</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>249.6733</v>
+        <v>249.6618</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3606,10 +3606,10 @@
         <v>718</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>8.1013</v>
+        <v>8.102</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>253.8168</v>
+        <v>253.8043</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3623,10 +3623,10 @@
         <v>720</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>7.8313</v>
+        <v>7.832</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>258.6533</v>
+        <v>258.6397</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3640,10 +3640,10 @@
         <v>722</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>7.5795</v>
+        <v>7.5801</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>264.0011</v>
+        <v>263.9865</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3657,10 +3657,10 @@
         <v>724</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>7.3335</v>
+        <v>7.3341</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>269.4105</v>
+        <v>269.3949</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
@@ -3674,10 +3674,10 @@
         <v>726</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>7.0472</v>
+        <v>7.0478</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>275.1816</v>
+        <v>275.1651</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3691,10 +3691,10 @@
         <v>728</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>6.825</v>
+        <v>6.8256</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>281.9144</v>
+        <v>281.8973</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3708,10 +3708,10 @@
         <v>730</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>6.5788</v>
+        <v>6.5792</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>288.7367</v>
+        <v>288.7193</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
@@ -3725,10 +3725,10 @@
         <v>732</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>6.3056</v>
+        <v>6.3059</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>295.7518</v>
+        <v>295.7344</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
@@ -3742,10 +3742,10 @@
         <v>734</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>6.09</v>
+        <v>6.0902</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>304.2208</v>
+        <v>304.2039</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
@@ -3762,7 +3762,7 @@
         <v>5.8656</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>312.8559</v>
+        <v>312.8402</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
@@ -3776,10 +3776,10 @@
         <v>738</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>5.6907</v>
+        <v>5.6905</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>321.9763</v>
+        <v>321.9626</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
@@ -3793,10 +3793,10 @@
         <v>740</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>5.5534</v>
+        <v>5.5531</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>331.6095</v>
+        <v>331.5984</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
@@ -3810,10 +3810,10 @@
         <v>742</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>5.4678</v>
+        <v>5.4675</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>341.7558</v>
+        <v>341.748</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
@@ -3827,10 +3827,10 @@
         <v>744</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>5.415</v>
+        <v>5.4146</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>352.1437</v>
+        <v>352.1396</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
@@ -3844,10 +3844,10 @@
         <v>746</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>5.4781</v>
+        <v>5.4777</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>2.3651</v>
+        <v>2.3649</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
@@ -3861,10 +3861,10 @@
         <v>748</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>5.5247</v>
+        <v>5.5244</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>12.3058</v>
+        <v>12.3094</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
@@ -3878,10 +3878,10 @@
         <v>750</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>5.6633</v>
+        <v>5.663</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>22.7192</v>
+        <v>22.726</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
@@ -3895,10 +3895,10 @@
         <v>752</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>5.8004</v>
+        <v>5.8003</v>
       </c>
       <c r="C203" s="2" t="n">
-        <v>31.6286</v>
+        <v>31.6381</v>
       </c>
       <c r="D203" s="2" t="n">
         <v>0.015</v>
@@ -3912,10 +3912,10 @@
         <v>754</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>5.9861</v>
+        <v>5.9862</v>
       </c>
       <c r="C204" s="2" t="n">
-        <v>40.3471</v>
+        <v>40.3586</v>
       </c>
       <c r="D204" s="2" t="n">
         <v>0.015</v>
@@ -3929,10 +3929,10 @@
         <v>756</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>6.2039</v>
+        <v>6.2041</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>48.393</v>
+        <v>48.4058</v>
       </c>
       <c r="D205" s="2" t="n">
         <v>0.015</v>
@@ -3946,10 +3946,10 @@
         <v>758</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>6.4463</v>
+        <v>6.4466</v>
       </c>
       <c r="C206" s="2" t="n">
-        <v>56.0525</v>
+        <v>56.066</v>
       </c>
       <c r="D206" s="2" t="n">
         <v>0.015</v>
@@ -3963,16 +3963,16 @@
         <v>760</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>6.7214</v>
+        <v>6.7218</v>
       </c>
       <c r="C207" s="2" t="n">
-        <v>63.2701</v>
+        <v>63.2839</v>
       </c>
       <c r="D207" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>0.1428</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="208">
@@ -3980,10 +3980,10 @@
         <v>762</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>6.9153</v>
+        <v>6.9158</v>
       </c>
       <c r="C208" s="2" t="n">
-        <v>69.6829</v>
+        <v>69.6966</v>
       </c>
       <c r="D208" s="2" t="n">
         <v>0.015</v>
@@ -3997,16 +3997,16 @@
         <v>764</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>7.1703</v>
+        <v>7.1708</v>
       </c>
       <c r="C209" s="2" t="n">
-        <v>75.4307</v>
+        <v>75.444</v>
       </c>
       <c r="D209" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.1334</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="210">
@@ -4014,10 +4014,10 @@
         <v>766</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>7.4127</v>
+        <v>7.4132</v>
       </c>
       <c r="C210" s="2" t="n">
-        <v>81.1206</v>
+        <v>81.13339999999999</v>
       </c>
       <c r="D210" s="2" t="n">
         <v>0.015</v>
@@ -4031,10 +4031,10 @@
         <v>768</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>7.6203</v>
+        <v>7.6209</v>
       </c>
       <c r="C211" s="2" t="n">
-        <v>86.04389999999999</v>
+        <v>86.05589999999999</v>
       </c>
       <c r="D211" s="2" t="n">
         <v>0.015</v>
@@ -4048,10 +4048,10 @@
         <v>770</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>7.827</v>
+        <v>7.8275</v>
       </c>
       <c r="C212" s="2" t="n">
-        <v>90.84610000000001</v>
+        <v>90.8574</v>
       </c>
       <c r="D212" s="2" t="n">
         <v>0.015</v>
@@ -4065,10 +4065,10 @@
         <v>772</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>8.045400000000001</v>
+        <v>8.0459</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>95.36369999999999</v>
+        <v>95.3741</v>
       </c>
       <c r="D213" s="2" t="n">
         <v>0.015</v>
@@ -4082,10 +4082,10 @@
         <v>774</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>8.2189</v>
+        <v>8.2194</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>99.56610000000001</v>
+        <v>99.5757</v>
       </c>
       <c r="D214" s="2" t="n">
         <v>0.015</v>
@@ -4099,10 +4099,10 @@
         <v>776</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>8.441000000000001</v>
+        <v>8.4415</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>103.3905</v>
+        <v>103.3995</v>
       </c>
       <c r="D215" s="2" t="n">
         <v>0.015</v>
@@ -4116,10 +4116,10 @@
         <v>778</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>8.626899999999999</v>
+        <v>8.6273</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>107.0062</v>
+        <v>107.0144</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>0.015</v>
@@ -4133,10 +4133,10 @@
         <v>780</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>8.824</v>
+        <v>8.824400000000001</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>110.2442</v>
+        <v>110.2517</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>0.015</v>
@@ -4150,10 +4150,10 @@
         <v>782</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>8.973000000000001</v>
+        <v>8.9733</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>113.6249</v>
+        <v>113.6318</v>
       </c>
       <c r="D218" s="2" t="n">
         <v>0.015</v>
@@ -4167,10 +4167,10 @@
         <v>784</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>9.1386</v>
+        <v>9.1389</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>116.6397</v>
+        <v>116.6459</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>0.015</v>
@@ -4184,10 +4184,10 @@
         <v>786</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>9.2798</v>
+        <v>9.280099999999999</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>119.5969</v>
+        <v>119.6026</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>0.015</v>
@@ -4201,10 +4201,10 @@
         <v>788</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>9.4369</v>
+        <v>9.437200000000001</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>122.6289</v>
+        <v>122.6341</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>0.015</v>
@@ -4218,10 +4218,10 @@
         <v>790</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>9.5594</v>
+        <v>9.559699999999999</v>
       </c>
       <c r="C222" s="2" t="n">
-        <v>125.0587</v>
+        <v>125.0634</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>0.015</v>
@@ -4235,10 +4235,10 @@
         <v>792</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>9.7224</v>
+        <v>9.7227</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>127.5171</v>
+        <v>127.5214</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>0.015</v>
@@ -4252,10 +4252,10 @@
         <v>794</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>9.830399999999999</v>
+        <v>9.8306</v>
       </c>
       <c r="C224" s="2" t="n">
-        <v>130.1525</v>
+        <v>130.1564</v>
       </c>
       <c r="D224" s="2" t="n">
         <v>0.015</v>
@@ -4269,10 +4269,10 @@
         <v>796</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>9.917899999999999</v>
+        <v>9.918100000000001</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>132.4185</v>
+        <v>132.4222</v>
       </c>
       <c r="D225" s="2" t="n">
         <v>0.015</v>
@@ -4286,10 +4286,10 @@
         <v>798</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>10.0526</v>
+        <v>10.0527</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>134.7311</v>
+        <v>134.7344</v>
       </c>
       <c r="D226" s="2" t="n">
         <v>0.015</v>
@@ -4303,10 +4303,10 @@
         <v>800</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>10.1432</v>
+        <v>10.1434</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>136.8555</v>
+        <v>136.8585</v>
       </c>
       <c r="D227" s="2" t="n">
         <v>0.015</v>
